--- a/docs/samples/contoh-import-tugas-akhir.xlsx
+++ b/docs/samples/contoh-import-tugas-akhir.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t>tanggal_mulai_tiket</t>
+          <t>tanggal_mulai_masa_aktif</t>
         </is>
       </c>
     </row>
